--- a/dataset/construct/dataset_splits/data_size/50_percent/tum/fold3.xlsx
+++ b/dataset/construct/dataset_splits/data_size/50_percent/tum/fold3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1314</v>
+        <v>2513</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,94 +625,94 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>79.1469129464852</v>
+        <v>84.37595016731311</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>24.6755002704164</v>
       </c>
       <c r="E2" t="n">
-        <v>31.833910034602</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>392.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1150</v>
+        <v>407.3</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>215.7</v>
       </c>
       <c r="K2" t="n">
-        <v>120.5</v>
+        <v>1015.4</v>
       </c>
       <c r="L2" t="n">
-        <v>175.9</v>
+        <v>52.4</v>
       </c>
       <c r="M2" t="n">
-        <v>229.1</v>
+        <v>28.3</v>
       </c>
       <c r="N2" t="n">
-        <v>525.5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>35.9</v>
+        <v>80.7</v>
       </c>
       <c r="P2" t="n">
-        <v>28.7</v>
+        <v>24.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>92.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>24.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>25.53</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>25.305576776165</v>
       </c>
       <c r="X2" t="n">
-        <v>23</v>
+        <v>25.0017500819378</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.270676691729323</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.2869875222816</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>23.3675988578761</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -739,22 +724,15 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>106</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>246</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1094</v>
+        <v>1306</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,79 +740,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74.44095254391971</v>
+        <v>86.2350005070094</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>21.6855368882395</v>
       </c>
       <c r="E3" t="n">
-        <v>25.3443526170798</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>10.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1550</v>
+        <v>136.9</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>420.7</v>
+        <v>220.2</v>
       </c>
       <c r="L3" t="n">
-        <v>199.2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>296.8</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>916.7</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>35.2</v>
+        <v>20.85</v>
       </c>
       <c r="V3" t="n">
-        <v>35.2</v>
+        <v>0.23</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>20.912910618793</v>
       </c>
       <c r="X3" t="n">
-        <v>23.25</v>
+        <v>20.4698827870943</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.204633204633205</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.3002291825821</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.8943655965997</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>1</v>
@@ -849,36 +827,27 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1572</v>
+        <v>2447</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,88 +855,88 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>86.5638272872462</v>
+        <v>88.5101123659594</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>23.3354661447551</v>
       </c>
       <c r="E4" t="n">
-        <v>24.8015873015873</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>695.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1650</v>
+        <v>297.9</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>255.1</v>
       </c>
       <c r="K4" t="n">
-        <v>117.8</v>
+        <v>1248.3</v>
       </c>
       <c r="L4" t="n">
-        <v>166</v>
+        <v>55.8</v>
       </c>
       <c r="M4" t="n">
-        <v>264.6</v>
+        <v>25.2</v>
       </c>
       <c r="N4" t="n">
-        <v>548.4</v>
+        <v>34.4</v>
       </c>
       <c r="O4" t="n">
-        <v>7.3</v>
+        <v>115.4</v>
       </c>
       <c r="P4" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>66.2</v>
+        <v>6.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>19.1</v>
+        <v>25.6</v>
       </c>
       <c r="V4" t="n">
-        <v>19.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>26.2923351158645</v>
       </c>
       <c r="X4" t="n">
-        <v>24.4</v>
+        <v>25.8576553751625</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.165413533834587</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>24.5098039215686</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.1181250506758</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -976,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -985,24 +954,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>192</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>505</v>
+        <v>467</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1010,123 +970,112 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>76.737962962963</v>
+        <v>80.3545252490684</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>34.7222222222222</v>
       </c>
       <c r="E5" t="n">
-        <v>21.8775510204081</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>37</v>
+        <v>319</v>
       </c>
       <c r="I5" t="n">
-        <v>14200</v>
+        <v>274</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>312</v>
       </c>
       <c r="K5" t="n">
-        <v>609</v>
+        <v>905</v>
       </c>
       <c r="L5" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="N5" t="n">
-        <v>1543</v>
+        <v>57</v>
       </c>
       <c r="O5" t="n">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="V5" t="n">
-        <v>66</v>
+        <v>0.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>28.9661319073084</v>
       </c>
       <c r="X5" t="n">
-        <v>26.5</v>
+        <v>28.31755269249</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.233333333333333</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>26.7379679144385</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>26.2896834807734</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>134</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>347</v>
+        <v>635</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1134,77 +1083,79 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>84.5302151304282</v>
+        <v>79.51356757167849</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>21.09375</v>
       </c>
       <c r="E6" t="n">
-        <v>27.0416441319632</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>45</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>523</v>
+      </c>
+      <c r="I6" t="n">
+        <v>178</v>
+      </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>279</v>
       </c>
       <c r="K6" t="n">
-        <v>346</v>
+        <v>980</v>
       </c>
       <c r="L6" t="n">
-        <v>162.8</v>
+        <v>96</v>
       </c>
       <c r="M6" t="n">
-        <v>134.3</v>
+        <v>65</v>
       </c>
       <c r="N6" t="n">
-        <v>643.1</v>
+        <v>58</v>
       </c>
       <c r="O6" t="n">
-        <v>39.2</v>
+        <v>219</v>
       </c>
       <c r="P6" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>48.8</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>8.6</v>
+        <v>23.9</v>
       </c>
       <c r="V6" t="n">
-        <v>46.8</v>
+        <v>0.22</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X6" t="n">
-        <v>26.4</v>
+        <v>23.5844721732425</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.197952218430034</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>26.4196587726</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>26.0831054612881</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1222,29 +1173,22 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1252,85 +1196,85 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86.0683245874211</v>
+        <v>74.1720111795574</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>25.9515570934256</v>
       </c>
       <c r="E7" t="n">
-        <v>21.484375</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="I7" t="n">
-        <v>882</v>
+        <v>215</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="K7" t="n">
-        <v>153</v>
+        <v>557</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="O7" t="n">
+        <v>68</v>
+      </c>
+      <c r="P7" t="n">
         <v>49</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>49</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X7" t="n">
-        <v>19.8</v>
+        <v>22.3940969210825</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.255506607929515</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.690094219506</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.1186577456453</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1339,36 +1283,27 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>78</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>182</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>324</v>
+        <v>472</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1376,83 +1311,85 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>82.3836315499278</v>
+        <v>82.9967864793267</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>19.2276878705335</v>
       </c>
       <c r="E8" t="n">
-        <v>29.585798816568</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>243</v>
+      </c>
+      <c r="I8" t="n">
+        <v>105</v>
+      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="K8" t="n">
-        <v>291</v>
+        <v>525</v>
       </c>
       <c r="L8" t="n">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>43</v>
+        <v>31.7</v>
       </c>
       <c r="N8" t="n">
-        <v>455</v>
+        <v>11</v>
       </c>
       <c r="O8" t="n">
-        <v>50</v>
+        <v>52.7</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" t="n">
         <v>2</v>
       </c>
-      <c r="R8" t="n">
-        <v>52</v>
-      </c>
-      <c r="S8" t="n">
-        <v>49</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>20.45</v>
       </c>
       <c r="V8" t="n">
-        <v>53</v>
+        <v>0.14</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>21.1675579322638</v>
       </c>
       <c r="X8" t="n">
-        <v>21.4</v>
+        <v>20.6802165106906</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.238683127572017</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.6450216450216</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>20.9857015385198</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1461,36 +1398,27 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>76</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>144</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>898</v>
+        <v>731</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1498,85 +1426,85 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>79.69788897127791</v>
+        <v>81.0275846705706</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>17.9163307354653</v>
       </c>
       <c r="E9" t="n">
-        <v>22.2222222222222</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>344</v>
       </c>
       <c r="I9" t="n">
-        <v>12100</v>
+        <v>266</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>261.4</v>
       </c>
       <c r="K9" t="n">
-        <v>91</v>
+        <v>871.4</v>
       </c>
       <c r="L9" t="n">
-        <v>74</v>
+        <v>5.7</v>
       </c>
       <c r="M9" t="n">
-        <v>71</v>
+        <v>11.5</v>
       </c>
       <c r="N9" t="n">
-        <v>236</v>
+        <v>33</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>50.2</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>23.15</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>23.2683982683983</v>
       </c>
       <c r="X9" t="n">
-        <v>22.2</v>
+        <v>22.7325659324369</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.165289256198347</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.9633307868602</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.9056486523839</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1597,24 +1525,15 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>148</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2031</v>
+        <v>624</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1622,79 +1541,79 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>85.6764691865034</v>
+        <v>90.1065803483155</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>20.0288415318058</v>
       </c>
       <c r="E10" t="n">
-        <v>27.7777777777777</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I10" t="n">
-        <v>882</v>
+        <v>45</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="K10" t="n">
-        <v>423.4</v>
+        <v>156</v>
       </c>
       <c r="L10" t="n">
-        <v>142.6</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>389.7</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>955.7</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>114.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>55.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>29.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>198.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>65.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>27.2</v>
+        <v>22.15</v>
       </c>
       <c r="V10" t="n">
-        <v>92.59999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X10" t="n">
-        <v>28.85</v>
+        <v>21.9926337013585</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.235474006116208</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>29.4435956200662</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>28.5191036537487</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1721,22 +1640,15 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>208</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
+        <v>200</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>458</v>
+        <v>937</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1744,79 +1656,79 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>87.1275439196897</v>
+        <v>81.4197179443304</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>22.0580511886838</v>
       </c>
       <c r="E11" t="n">
-        <v>24.9770431588613</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>52</v>
+        <v>177</v>
       </c>
       <c r="I11" t="n">
-        <v>35000</v>
+        <v>167</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="K11" t="n">
-        <v>746</v>
+        <v>377</v>
       </c>
       <c r="L11" t="n">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>797</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>2275</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="P11" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>486</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>209</v>
+        <v>22.45</v>
       </c>
       <c r="V11" t="n">
-        <v>285</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X11" t="n">
-        <v>25.55</v>
+        <v>22.0792760606539</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.237931034482759</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>25.9421950598421</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>25.4282983710565</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1834,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -1843,24 +1755,15 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>104</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>598</v>
+        <v>1672</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1868,85 +1771,85 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>80.29658529165719</v>
+        <v>85.7315332281289</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>26.0789715335169</v>
       </c>
       <c r="E12" t="n">
-        <v>17.0068027210884</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="I12" t="n">
-        <v>1630</v>
+        <v>52</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>238</v>
       </c>
       <c r="L12" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>69</v>
+        <v>24.2</v>
       </c>
       <c r="V12" t="n">
-        <v>74</v>
+        <v>0.27</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X12" t="n">
-        <v>19.8</v>
+        <v>23.3675988578761</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.7351667939903</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>19.1461601132455</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -1955,10 +1858,10 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -1967,24 +1870,15 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>180</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1992,83 +1886,85 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>75.4179690470758</v>
+        <v>80.5730949121606</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>26.2975778546712</v>
       </c>
       <c r="E13" t="n">
-        <v>34.220041322314</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>483.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>564.9</v>
+      </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>380.1</v>
       </c>
       <c r="K13" t="n">
-        <v>378</v>
+        <v>1428.4</v>
       </c>
       <c r="L13" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>340</v>
+        <v>13.8</v>
       </c>
       <c r="N13" t="n">
-        <v>1116</v>
+        <v>19.1</v>
       </c>
       <c r="O13" t="n">
-        <v>36</v>
+        <v>32.90000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>26.35</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>26.5469824293354</v>
       </c>
       <c r="X13" t="n">
-        <v>27.2</v>
+        <v>26.0806653934161</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.155932203389831</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.7379679144385</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>26.2896834807734</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2080,33 +1976,24 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>515</v>
+        <v>2192</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2114,79 +2001,79 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>78.3007491063959</v>
+        <v>83.62327093948841</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>26.9896193771626</v>
       </c>
       <c r="E14" t="n">
-        <v>23.2356317012401</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>60</v>
+        <v>80.7</v>
       </c>
       <c r="I14" t="n">
-        <v>3550</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>32.9</v>
       </c>
       <c r="K14" t="n">
-        <v>629</v>
+        <v>113.6</v>
       </c>
       <c r="L14" t="n">
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1811</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>21.6768525592055</v>
       </c>
       <c r="X14" t="n">
-        <v>27.75</v>
+        <v>20.6555825335006</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.292307692307692</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>27.947542653425</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>26.973142863685</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2207,30 +2094,19 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>242</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="AK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2238,79 +2114,79 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>78.96926572362921</v>
+        <v>80.4444026161685</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>38.7396694214876</v>
       </c>
       <c r="E15" t="n">
-        <v>27.7551020408163</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>966</v>
       </c>
       <c r="I15" t="n">
-        <v>152</v>
+        <v>1037</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>221</v>
       </c>
       <c r="K15" t="n">
-        <v>114</v>
+        <v>2224</v>
       </c>
       <c r="L15" t="n">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="M15" t="n">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="N15" t="n">
-        <v>400</v>
+        <v>18</v>
       </c>
       <c r="O15" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="P15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>46</v>
+        <v>29.95</v>
       </c>
       <c r="V15" t="n">
-        <v>46</v>
+        <v>0.26</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>31.5126050420168</v>
       </c>
       <c r="X15" t="n">
-        <v>21.3</v>
+        <v>30.3986119121575</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.3359375</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.4357677787856</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2322,39 +2198,28 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>180</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>544</v>
+        <v>360</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2362,79 +2227,79 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>86.9331313534616</v>
+        <v>85.260315042969</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>28.6501377410468</v>
       </c>
       <c r="E16" t="n">
-        <v>29.5525494276795</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>40</v>
+        <v>187</v>
       </c>
       <c r="I16" t="n">
-        <v>30900</v>
+        <v>294</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="K16" t="n">
-        <v>256</v>
+        <v>619</v>
       </c>
       <c r="L16" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>23.05</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>23.554876496053</v>
       </c>
       <c r="X16" t="n">
-        <v>21.75</v>
+        <v>23.176170013362</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.313953488372093</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>22.7591036414566</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>21.3763064498772</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2443,42 +2308,31 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>116</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>208</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="AK16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1154</v>
+        <v>587</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2486,79 +2340,79 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>84.58157277486249</v>
+        <v>79.70262377367099</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>36.7309458218549</v>
       </c>
       <c r="E17" t="n">
-        <v>23.7654320987654</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>850</v>
       </c>
       <c r="I17" t="n">
-        <v>11300</v>
+        <v>538</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="K17" t="n">
-        <v>274.1</v>
+        <v>2189</v>
       </c>
       <c r="L17" t="n">
-        <v>300.4</v>
+        <v>32</v>
       </c>
       <c r="M17" t="n">
-        <v>298.1</v>
+        <v>23</v>
       </c>
       <c r="N17" t="n">
-        <v>872.6</v>
+        <v>25</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>31.1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>31.1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>23.75</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>23.554876496053</v>
       </c>
       <c r="X17" t="n">
-        <v>28.2</v>
+        <v>22.8721164508225</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.231974921630094</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>28.4568372803667</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>28.0442958618834</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2585,22 +2439,15 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN17" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>636</v>
+        <v>579</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2608,79 +2455,79 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>81.9098752756864</v>
+        <v>79.1056030876873</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>25.390625</v>
       </c>
       <c r="E18" t="n">
-        <v>31.25</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>50</v>
+        <v>282</v>
       </c>
       <c r="I18" t="n">
-        <v>2600</v>
+        <v>283</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>266</v>
       </c>
       <c r="K18" t="n">
-        <v>607.7</v>
+        <v>831</v>
       </c>
       <c r="L18" t="n">
-        <v>229.5</v>
+        <v>158</v>
       </c>
       <c r="M18" t="n">
-        <v>268.5</v>
+        <v>41</v>
       </c>
       <c r="N18" t="n">
-        <v>1105.7</v>
+        <v>77</v>
       </c>
       <c r="O18" t="n">
-        <v>26.8</v>
+        <v>276</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q18" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>47.1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>24.5098039215686</v>
       </c>
       <c r="X18" t="n">
-        <v>24.45</v>
+        <v>23.8260951566085</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.08984375</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>24.3824802648332</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>24.1734751727661</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2701,30 +2548,21 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN18" t="n">
         <v>146</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1356</v>
+        <v>2006</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2732,80 +2570,82 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>78.99659071032021</v>
+        <v>67.10314342662311</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>33.8123415046491</v>
       </c>
       <c r="E19" t="n">
-        <v>23.9868703446534</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>718.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1023.4</v>
+      </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>535.8</v>
       </c>
       <c r="K19" t="n">
-        <v>404.3</v>
+        <v>2277.8</v>
       </c>
       <c r="L19" t="n">
-        <v>263.5</v>
+        <v>52</v>
       </c>
       <c r="M19" t="n">
-        <v>383.3</v>
+        <v>140.7</v>
       </c>
       <c r="N19" t="n">
-        <v>1051.1</v>
+        <v>59.7</v>
       </c>
       <c r="O19" t="n">
-        <v>36.6</v>
+        <v>252.4</v>
       </c>
       <c r="P19" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>13.7</v>
+        <v>100.6</v>
       </c>
       <c r="R19" t="n">
-        <v>56.6</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>105.6</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>27.2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>27.6610644257703</v>
       </c>
       <c r="X19" t="n">
-        <v>27.95</v>
+        <v>27.3480481672903</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.236593059936909</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>27.7565571683219</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>27.2874765576698</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2814,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -2829,22 +2669,15 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN19" t="inlineStr"/>
+        <v>226</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>638</v>
+        <v>987</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2852,77 +2685,79 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>72.7814039090425</v>
+        <v>84.6664857910614</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>26.5118040651432</v>
       </c>
       <c r="E20" t="n">
-        <v>29.7265160523186</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>446</v>
+      </c>
+      <c r="I20" t="n">
+        <v>183</v>
+      </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="K20" t="n">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="L20" t="n">
-        <v>426</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>413</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1514</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>31</v>
+        <v>25.7</v>
       </c>
       <c r="V20" t="n">
-        <v>31</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>25.7830404889228</v>
       </c>
       <c r="X20" t="n">
-        <v>27.1</v>
+        <v>25.4533139190353</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.143835616438356</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>27.0562770562771</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>26.7694618135822</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2931,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2940,31 +2775,24 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>116</v>
-      </c>
-      <c r="AN20" t="inlineStr"/>
+        <v>244</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2972,88 +2800,88 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>82.4873716632443</v>
+        <v>86.8191345349456</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>25.6055363321799</v>
       </c>
       <c r="E21" t="n">
-        <v>24.4897959183673</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>50</v>
+        <v>420</v>
       </c>
       <c r="I21" t="n">
-        <v>18300</v>
+        <v>285</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>308</v>
       </c>
       <c r="K21" t="n">
-        <v>694</v>
+        <v>1013</v>
       </c>
       <c r="L21" t="n">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1059</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2609</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="V21" t="n">
-        <v>11</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>23.554876496053</v>
       </c>
       <c r="X21" t="n">
-        <v>25.3</v>
+        <v>23.4220054480732</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.255172413793103</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>26.4196587726</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>25.6028939368547</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3062,31 +2890,24 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN21" t="inlineStr"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>516</v>
+        <v>1109</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3094,121 +2915,114 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>82.09534185109131</v>
+        <v>79.1909800174918</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>28.3937263385613</v>
       </c>
       <c r="E22" t="n">
-        <v>29.0256076388888</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="I22" t="n">
-        <v>2800</v>
+        <v>173</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="K22" t="n">
-        <v>797</v>
+        <v>518</v>
       </c>
       <c r="L22" t="n">
-        <v>410</v>
+        <v>24</v>
       </c>
       <c r="M22" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1631</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="P22" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>247</v>
+        <v>33</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="T22" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V22" t="n">
-        <v>9</v>
+        <v>0.21</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>30.2393684746626</v>
       </c>
       <c r="X22" t="n">
-        <v>25</v>
+        <v>29.7425256555005</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.257839721254355</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>25.1464222052457</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>24.6143810163112</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>194</v>
-      </c>
-      <c r="AN22" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3216,77 +3030,79 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>85.91221886328491</v>
+        <v>82.3836315499278</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>29.585798816568</v>
       </c>
       <c r="E23" t="n">
-        <v>25.8805706350208</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>45</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>291</v>
+      </c>
+      <c r="I23" t="n">
+        <v>121</v>
+      </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="K23" t="n">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="L23" t="n">
-        <v>378</v>
+        <v>50</v>
       </c>
       <c r="M23" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1013</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
         <v>52</v>
       </c>
       <c r="P23" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>21.4</v>
       </c>
       <c r="V23" t="n">
-        <v>33</v>
+        <v>0.24</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>21.6450216450216</v>
       </c>
       <c r="X23" t="n">
-        <v>29.3</v>
+        <v>20.9857015385198</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.16875</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>28.9661319073084</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>28.6082260699118</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3313,24 +3129,15 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AK23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>254</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3338,85 +3145,91 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>73.3180274799098</v>
+        <v>85.82740633001239</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>29.0659268067115</v>
       </c>
       <c r="E24" t="n">
-        <v>28.0379234593594</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>60</v>
+        <v>1675</v>
       </c>
       <c r="I24" t="n">
-        <v>479</v>
+        <v>1134</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>1007</v>
       </c>
       <c r="K24" t="n">
-        <v>783</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
+        <v>3816</v>
+      </c>
+      <c r="L24" t="n">
+        <v>371</v>
+      </c>
       <c r="M24" t="n">
-        <v>684</v>
+        <v>124</v>
       </c>
       <c r="N24" t="n">
-        <v>1467</v>
+        <v>316</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
+        <v>811</v>
+      </c>
+      <c r="P24" t="n">
+        <v>155</v>
+      </c>
       <c r="Q24" t="n">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="R24" t="n">
-        <v>86</v>
+        <v>191</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="inlineStr"/>
+        <v>358</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
       <c r="U24" t="n">
-        <v>24</v>
+        <v>26.4</v>
       </c>
       <c r="V24" t="n">
-        <v>24</v>
+        <v>0.16</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>26.4196587726</v>
       </c>
       <c r="X24" t="n">
-        <v>23.25</v>
+        <v>26.3138801572997</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.102040816326531</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>23.4491614055397</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3425,30 +3238,21 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>104</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>212</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2886</v>
+        <v>719</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3456,79 +3260,79 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>87.4232017960808</v>
+        <v>80.36810593961521</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>20.1955782312925</v>
       </c>
       <c r="E25" t="n">
-        <v>31.3145661157024</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="I25" t="n">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="K25" t="n">
-        <v>569</v>
+        <v>183</v>
       </c>
       <c r="L25" t="n">
-        <v>741</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>592</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1902</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V25" t="n">
-        <v>93</v>
+        <v>0.24</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>23.4912146676853</v>
       </c>
       <c r="X25" t="n">
-        <v>24.35</v>
+        <v>22.7605444857119</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.196296296296296</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>23.9686783804431</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>23.3675988578761</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3546,33 +3350,24 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>212</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1131</v>
+        <v>1962</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3580,91 +3375,91 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>84.27193794838639</v>
+        <v>74.1123504322255</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>25.0593070266296</v>
       </c>
       <c r="E26" t="n">
-        <v>28.2283864654296</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>60</v>
+        <v>783.1</v>
       </c>
       <c r="I26" t="n">
-        <v>2740</v>
+        <v>744.9</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="K26" t="n">
-        <v>151</v>
+        <v>1697</v>
       </c>
       <c r="L26" t="n">
-        <v>171</v>
+        <v>0.4</v>
       </c>
       <c r="M26" t="n">
-        <v>116</v>
+        <v>196.2</v>
       </c>
       <c r="N26" t="n">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>196.6</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>28.15</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>28.5841609371021</v>
       </c>
       <c r="X26" t="n">
-        <v>25.15</v>
+        <v>28.1846427181971</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.235087719298246</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>25.4647313470843</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>24.8459903311873</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3673,28 +3468,21 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN26" t="inlineStr"/>
+        <v>156</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2413</v>
+        <v>2488</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3702,79 +3490,79 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>83.4834113494055</v>
+        <v>86.902992211068</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>23.191094619666</v>
       </c>
       <c r="E27" t="n">
-        <v>37.6542220797949</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>60</v>
+        <v>55.2</v>
       </c>
       <c r="I27" t="n">
-        <v>425</v>
+        <v>37.3</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>28.1</v>
       </c>
       <c r="K27" t="n">
-        <v>1003.9</v>
+        <v>120.6</v>
       </c>
       <c r="L27" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
         <v>22.2</v>
       </c>
-      <c r="N27" t="n">
-        <v>1109.1</v>
-      </c>
-      <c r="O27" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>42</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>22.0588235294118</v>
       </c>
       <c r="X27" t="n">
-        <v>22.55</v>
+        <v>21.7540506465255</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.285171102661597</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.1729055258467</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>22.6034185328367</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3789,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -3801,19 +3589,10 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>162</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>220</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
